--- a/code/cmb/highl_so_fisher.xlsx
+++ b/code/cmb/highl_so_fisher.xlsx
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213222518.4445235</v>
+        <v>209754805.387334</v>
       </c>
       <c r="C2" t="n">
-        <v>-751647423.0604701</v>
+        <v>-736617077.9930127</v>
       </c>
       <c r="D2" t="n">
-        <v>163734142.617811</v>
+        <v>161324193.0909443</v>
       </c>
       <c r="E2" t="n">
-        <v>-5241473.904236572</v>
+        <v>-5085606.770791579</v>
       </c>
       <c r="F2" t="n">
-        <v>-67349876.98027775</v>
+        <v>-66351754.96717035</v>
       </c>
       <c r="G2" t="n">
-        <v>-14617623.7374079</v>
+        <v>-14419016.1710433</v>
       </c>
       <c r="H2" t="n">
-        <v>-7587888.965251675</v>
+        <v>-7457760.972205499</v>
       </c>
       <c r="I2" t="n">
-        <v>52393814.31534824</v>
+        <v>51631249.50266753</v>
       </c>
       <c r="J2" t="n">
-        <v>1628527.685388624</v>
+        <v>1528002.905541063</v>
       </c>
       <c r="K2" t="n">
-        <v>-12064.09565288469</v>
+        <v>-32729.89549263215</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-751647423.0604701</v>
+        <v>-736617077.9930127</v>
       </c>
       <c r="C3" t="n">
-        <v>3037087198.742686</v>
+        <v>2964721657.027106</v>
       </c>
       <c r="D3" t="n">
-        <v>-530347797.2286788</v>
+        <v>-521207328.0730313</v>
       </c>
       <c r="E3" t="n">
-        <v>32583745.31294829</v>
+        <v>31751795.49156612</v>
       </c>
       <c r="F3" t="n">
-        <v>242217717.5345786</v>
+        <v>237498313.0175204</v>
       </c>
       <c r="G3" t="n">
-        <v>51567757.40345956</v>
+        <v>50591485.70606548</v>
       </c>
       <c r="H3" t="n">
-        <v>25579312.98860566</v>
+        <v>25071498.31697514</v>
       </c>
       <c r="I3" t="n">
-        <v>-186868728.092315</v>
+        <v>-183263843.8253934</v>
       </c>
       <c r="J3" t="n">
-        <v>-7313611.64181344</v>
+        <v>-7060988.246351704</v>
       </c>
       <c r="K3" t="n">
-        <v>-364184.2727531569</v>
+        <v>-326826.5613221443</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>163734142.617811</v>
+        <v>161324193.0909443</v>
       </c>
       <c r="C4" t="n">
-        <v>-530347797.2286788</v>
+        <v>-521207328.0730313</v>
       </c>
       <c r="D4" t="n">
-        <v>135984266.5472721</v>
+        <v>134016376.8761793</v>
       </c>
       <c r="E4" t="n">
-        <v>-2462023.387088359</v>
+        <v>-2385568.844892902</v>
       </c>
       <c r="F4" t="n">
-        <v>-46630723.95752121</v>
+        <v>-46066398.27598455</v>
       </c>
       <c r="G4" t="n">
-        <v>-9709242.319021974</v>
+        <v>-9611528.284513641</v>
       </c>
       <c r="H4" t="n">
-        <v>-6460196.769922125</v>
+        <v>-6352948.429070017</v>
       </c>
       <c r="I4" t="n">
-        <v>36327436.3527712</v>
+        <v>35899069.45258789</v>
       </c>
       <c r="J4" t="n">
-        <v>3665138.923220088</v>
+        <v>3529059.056790321</v>
       </c>
       <c r="K4" t="n">
-        <v>678529.2949363026</v>
+        <v>645348.305028373</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5241473.904236572</v>
+        <v>-5085606.770791579</v>
       </c>
       <c r="C5" t="n">
-        <v>32583745.31294829</v>
+        <v>31751795.49156612</v>
       </c>
       <c r="D5" t="n">
-        <v>-2462023.387088359</v>
+        <v>-2385568.844892902</v>
       </c>
       <c r="E5" t="n">
-        <v>1065676.565878784</v>
+        <v>1051931.70821937</v>
       </c>
       <c r="F5" t="n">
-        <v>1878202.126073538</v>
+        <v>1820934.253376984</v>
       </c>
       <c r="G5" t="n">
-        <v>360460.9097760745</v>
+        <v>347659.3830884406</v>
       </c>
       <c r="H5" t="n">
-        <v>126692.2137338636</v>
+        <v>122766.2845291977</v>
       </c>
       <c r="I5" t="n">
-        <v>-1417096.694813157</v>
+        <v>-1372304.584457705</v>
       </c>
       <c r="J5" t="n">
-        <v>-125185.2348517038</v>
+        <v>-126811.9072100159</v>
       </c>
       <c r="K5" t="n">
-        <v>-21563.13684401158</v>
+        <v>-22393.97967375197</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-67349876.98027775</v>
+        <v>-66351754.96717035</v>
       </c>
       <c r="C6" t="n">
-        <v>242217717.5345786</v>
+        <v>237498313.0175204</v>
       </c>
       <c r="D6" t="n">
-        <v>-46630723.95752121</v>
+        <v>-46066398.27598455</v>
       </c>
       <c r="E6" t="n">
-        <v>1878202.126073537</v>
+        <v>1820934.253376984</v>
       </c>
       <c r="F6" t="n">
-        <v>26285495.4801174</v>
+        <v>25906877.09272526</v>
       </c>
       <c r="G6" t="n">
-        <v>6210779.757275067</v>
+        <v>6125520.958788337</v>
       </c>
       <c r="H6" t="n">
-        <v>1859764.539558041</v>
+        <v>1832806.506664289</v>
       </c>
       <c r="I6" t="n">
-        <v>-20428222.43863392</v>
+        <v>-20140216.07240312</v>
       </c>
       <c r="J6" t="n">
-        <v>2167894.097964704</v>
+        <v>2150257.387225226</v>
       </c>
       <c r="K6" t="n">
-        <v>763450.3294274576</v>
+        <v>756202.9498535765</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-14617623.7374079</v>
+        <v>-14419016.1710433</v>
       </c>
       <c r="C7" t="n">
-        <v>51567757.40345956</v>
+        <v>50591485.70606548</v>
       </c>
       <c r="D7" t="n">
-        <v>-9709242.319021974</v>
+        <v>-9611528.284513641</v>
       </c>
       <c r="E7" t="n">
-        <v>360460.9097760745</v>
+        <v>347659.3830884406</v>
       </c>
       <c r="F7" t="n">
-        <v>6210779.757275067</v>
+        <v>6125520.958788337</v>
       </c>
       <c r="G7" t="n">
-        <v>1522840.06535094</v>
+        <v>1502622.836429135</v>
       </c>
       <c r="H7" t="n">
-        <v>349607.1561685516</v>
+        <v>345449.2714611806</v>
       </c>
       <c r="I7" t="n">
-        <v>-4852816.823231066</v>
+        <v>-4787441.754210099</v>
       </c>
       <c r="J7" t="n">
-        <v>775796.1818934502</v>
+        <v>766818.2389284241</v>
       </c>
       <c r="K7" t="n">
-        <v>252016.3349019448</v>
+        <v>249023.0242437642</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7587888.965251675</v>
+        <v>-7457760.972205499</v>
       </c>
       <c r="C8" t="n">
-        <v>25579312.98860566</v>
+        <v>25071498.31697514</v>
       </c>
       <c r="D8" t="n">
-        <v>-6460196.769922125</v>
+        <v>-6352948.429070017</v>
       </c>
       <c r="E8" t="n">
-        <v>126692.2137338636</v>
+        <v>122766.2845291977</v>
       </c>
       <c r="F8" t="n">
-        <v>1859764.53955804</v>
+        <v>1832806.506664289</v>
       </c>
       <c r="G8" t="n">
-        <v>349607.1561685516</v>
+        <v>345449.2714611806</v>
       </c>
       <c r="H8" t="n">
-        <v>330658.9288338865</v>
+        <v>324495.8160776406</v>
       </c>
       <c r="I8" t="n">
-        <v>-1444107.538083015</v>
+        <v>-1423665.270108533</v>
       </c>
       <c r="J8" t="n">
-        <v>-343313.0565982815</v>
+        <v>-334079.6314019204</v>
       </c>
       <c r="K8" t="n">
-        <v>-80478.41995754027</v>
+        <v>-78153.30511710989</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52393814.31534824</v>
+        <v>51631249.50266753</v>
       </c>
       <c r="C9" t="n">
-        <v>-186868728.092315</v>
+        <v>-183263843.8253934</v>
       </c>
       <c r="D9" t="n">
-        <v>36327436.3527712</v>
+        <v>35899069.45258789</v>
       </c>
       <c r="E9" t="n">
-        <v>-1417096.694813157</v>
+        <v>-1372304.584457705</v>
       </c>
       <c r="F9" t="n">
-        <v>-20428222.43863392</v>
+        <v>-20140216.07240312</v>
       </c>
       <c r="G9" t="n">
-        <v>-4852816.823231066</v>
+        <v>-4787441.754210099</v>
       </c>
       <c r="H9" t="n">
-        <v>-1444107.538083015</v>
+        <v>-1423665.270108533</v>
       </c>
       <c r="I9" t="n">
-        <v>15956591.68373458</v>
+        <v>15735307.49603009</v>
       </c>
       <c r="J9" t="n">
-        <v>-1734773.832862999</v>
+        <v>-1720737.517423396</v>
       </c>
       <c r="K9" t="n">
-        <v>-607741.7893111182</v>
+        <v>-602035.9206606866</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1628527.685388624</v>
+        <v>1528002.905541063</v>
       </c>
       <c r="C10" t="n">
-        <v>-7313611.641813438</v>
+        <v>-7060988.246351703</v>
       </c>
       <c r="D10" t="n">
-        <v>3665138.923220088</v>
+        <v>3529059.056790321</v>
       </c>
       <c r="E10" t="n">
-        <v>-125185.2348517038</v>
+        <v>-126811.9072100159</v>
       </c>
       <c r="F10" t="n">
-        <v>2167894.097964704</v>
+        <v>2150257.387225226</v>
       </c>
       <c r="G10" t="n">
-        <v>775796.1818934502</v>
+        <v>766818.2389284241</v>
       </c>
       <c r="H10" t="n">
-        <v>-343313.0565982815</v>
+        <v>-334079.6314019204</v>
       </c>
       <c r="I10" t="n">
-        <v>-1734773.832862999</v>
+        <v>-1720737.517423396</v>
       </c>
       <c r="J10" t="n">
-        <v>1536576.684205067</v>
+        <v>1509054.112298143</v>
       </c>
       <c r="K10" t="n">
-        <v>431062.5877598944</v>
+        <v>423488.5199397432</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-12064.09565288466</v>
+        <v>-32729.89549263206</v>
       </c>
       <c r="C11" t="n">
-        <v>-364184.2727531568</v>
+        <v>-326826.5613221441</v>
       </c>
       <c r="D11" t="n">
-        <v>678529.2949363026</v>
+        <v>645348.305028373</v>
       </c>
       <c r="E11" t="n">
-        <v>-21563.13684401157</v>
+        <v>-22393.97967375196</v>
       </c>
       <c r="F11" t="n">
-        <v>763450.3294274576</v>
+        <v>756202.9498535765</v>
       </c>
       <c r="G11" t="n">
-        <v>252016.3349019449</v>
+        <v>249023.0242437641</v>
       </c>
       <c r="H11" t="n">
-        <v>-80478.41995754027</v>
+        <v>-78153.30511710989</v>
       </c>
       <c r="I11" t="n">
-        <v>-607741.7893111181</v>
+        <v>-602035.9206606866</v>
       </c>
       <c r="J11" t="n">
-        <v>431062.5877598944</v>
+        <v>423488.5199397432</v>
       </c>
       <c r="K11" t="n">
-        <v>121975.7560270279</v>
+        <v>119875.5277833252</v>
       </c>
     </row>
   </sheetData>
